--- a/Scout/waukee-vs-dcg-092526.xlsx
+++ b/Scout/waukee-vs-dcg-092526.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R6cfc8d6fae3a486d"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R1e1822576c5f46a3"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -124,12 +136,18 @@
     <t>Incomplete</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
     <t>TWINS WING</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -142,12 +160,18 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>FAR</t>
   </si>
   <si>
     <t>KEY 1</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
     <t>TWINS OPEN</t>
   </si>
   <si>
@@ -193,12 +217,18 @@
     <t>STICK</t>
   </si>
   <si>
+    <t>T UNDER</t>
+  </si>
+  <si>
     <t>SPLIT</t>
   </si>
   <si>
     <t>LOAD</t>
   </si>
   <si>
+    <t>GUN STACK K</t>
+  </si>
+  <si>
     <t>BOOT @ 8</t>
   </si>
   <si>
@@ -283,14 +313,20 @@
     <t>Rush, TD</t>
   </si>
   <si>
+    <t>GUN EVEN</t>
+  </si>
+  <si>
     <t>WING</t>
+  </si>
+  <si>
+    <t>K GUN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y148"/>
+  <dimension ref="A1:AC148"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -368,6 +404,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -377,19 +425,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -400,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -412,30 +460,33 @@
         <v>-29</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -447,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -459,30 +510,33 @@
         <v>-32</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U4" t="s">
-        <v>37</v>
-      </c>
-      <c r="X4">
+        <v>37</v>
+      </c>
+      <c r="P4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -494,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -506,27 +560,30 @@
         <v>-32</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s">
-        <v>37</v>
-      </c>
-      <c r="X5">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -538,7 +595,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -550,15 +607,15 @@
         <v>-32</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6">
+        <v>32</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -570,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -582,33 +639,36 @@
         <v>-43</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" t="s">
-        <v>44</v>
-      </c>
-      <c r="U7" t="s">
-        <v>30</v>
-      </c>
-      <c r="X7">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
+        <v>49</v>
+      </c>
+      <c r="W7" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -620,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -632,36 +692,39 @@
         <v>-48</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" t="s">
-        <v>30</v>
-      </c>
-      <c r="V8" t="s">
-        <v>37</v>
-      </c>
-      <c r="X8">
+        <v>37</v>
+      </c>
+      <c r="P8" t="s">
+        <v>52</v>
+      </c>
+      <c r="W8" t="s">
+        <v>42</v>
+      </c>
+      <c r="X8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -673,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -685,36 +748,39 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" t="s">
         <v>49</v>
       </c>
-      <c r="T9" t="s">
-        <v>50</v>
-      </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" t="s">
-        <v>30</v>
-      </c>
-      <c r="X9">
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -726,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -738,33 +804,36 @@
         <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J10">
         <v>-5</v>
       </c>
       <c r="K10" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" t="s">
         <v>49</v>
       </c>
-      <c r="T10" t="s">
-        <v>51</v>
-      </c>
-      <c r="U10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10">
+      <c r="W10" t="s">
+        <v>34</v>
+      </c>
+      <c r="X10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -776,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -788,30 +857,33 @@
         <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11" t="s">
-        <v>53</v>
-      </c>
-      <c r="T11" t="s">
-        <v>50</v>
-      </c>
-      <c r="U11" t="s">
-        <v>37</v>
-      </c>
-      <c r="X11">
+        <v>56</v>
+      </c>
+      <c r="P11" t="s">
+        <v>49</v>
+      </c>
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -823,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -835,30 +907,33 @@
         <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" t="s">
-        <v>34</v>
-      </c>
-      <c r="U12" t="s">
-        <v>37</v>
-      </c>
-      <c r="X12">
+        <v>37</v>
+      </c>
+      <c r="P12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12">
         <v>2</v>
       </c>
     </row>
@@ -870,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -882,30 +957,33 @@
         <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J13">
         <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13" t="s">
-        <v>37</v>
-      </c>
-      <c r="S13" t="s">
-        <v>54</v>
-      </c>
-      <c r="U13" t="s">
-        <v>37</v>
-      </c>
-      <c r="X13">
+        <v>56</v>
+      </c>
+      <c r="P13" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB13">
         <v>2</v>
       </c>
     </row>
@@ -917,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -929,30 +1007,33 @@
         <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J14">
         <v>-11</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S14" t="s">
-        <v>43</v>
-      </c>
-      <c r="U14" t="s">
-        <v>37</v>
-      </c>
-      <c r="X14">
+        <v>37</v>
+      </c>
+      <c r="P14" t="s">
+        <v>49</v>
+      </c>
+      <c r="W14" t="s">
+        <v>34</v>
+      </c>
+      <c r="X14" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB14">
         <v>2</v>
       </c>
     </row>
@@ -964,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -976,30 +1057,33 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" t="s">
-        <v>39</v>
-      </c>
-      <c r="S15" t="s">
-        <v>55</v>
-      </c>
-      <c r="U15" t="s">
-        <v>30</v>
-      </c>
-      <c r="X15">
+        <v>37</v>
+      </c>
+      <c r="P15" t="s">
+        <v>44</v>
+      </c>
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15">
         <v>2</v>
       </c>
     </row>
@@ -1011,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1023,30 +1107,33 @@
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" t="s">
-        <v>30</v>
-      </c>
-      <c r="X16">
+        <v>37</v>
+      </c>
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="W16" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -1058,7 +1145,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1070,15 +1157,15 @@
         <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
-      </c>
-      <c r="X17">
+        <v>64</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1090,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1102,33 +1189,36 @@
         <v>-17</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J18">
         <v>8</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" t="s">
-        <v>30</v>
-      </c>
-      <c r="S18" t="s">
-        <v>43</v>
-      </c>
-      <c r="T18" t="s">
-        <v>57</v>
-      </c>
-      <c r="U18" t="s">
-        <v>30</v>
-      </c>
-      <c r="X18">
+        <v>37</v>
+      </c>
+      <c r="P18" t="s">
+        <v>49</v>
+      </c>
+      <c r="W18" t="s">
+        <v>34</v>
+      </c>
+      <c r="X18" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1140,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1152,36 +1242,39 @@
         <v>-25</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J19">
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" t="s">
-        <v>37</v>
-      </c>
-      <c r="S19" t="s">
-        <v>45</v>
-      </c>
-      <c r="T19" t="s">
-        <v>58</v>
-      </c>
-      <c r="U19" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19" t="s">
-        <v>37</v>
-      </c>
-      <c r="X19">
+        <v>37</v>
+      </c>
+      <c r="P19" t="s">
+        <v>52</v>
+      </c>
+      <c r="W19" t="s">
+        <v>42</v>
+      </c>
+      <c r="X19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1193,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1205,33 +1298,36 @@
         <v>-33</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J20">
         <v>8</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" t="s">
-        <v>30</v>
-      </c>
-      <c r="S20" t="s">
-        <v>43</v>
-      </c>
-      <c r="T20" t="s">
-        <v>59</v>
-      </c>
-      <c r="U20" t="s">
-        <v>30</v>
-      </c>
-      <c r="X20">
+        <v>37</v>
+      </c>
+      <c r="P20" t="s">
+        <v>49</v>
+      </c>
+      <c r="W20" t="s">
+        <v>34</v>
+      </c>
+      <c r="X20" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1243,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1255,36 +1351,39 @@
         <v>-41</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R21" t="s">
-        <v>37</v>
-      </c>
-      <c r="S21" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U21" t="s">
-        <v>30</v>
-      </c>
-      <c r="V21" t="s">
-        <v>30</v>
-      </c>
-      <c r="X21">
+        <v>56</v>
+      </c>
+      <c r="P21" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21" t="s">
+        <v>42</v>
+      </c>
+      <c r="X21" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1296,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1308,33 +1407,36 @@
         <v>-41</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
-      </c>
-      <c r="R22" t="s">
-        <v>30</v>
-      </c>
-      <c r="S22" t="s">
-        <v>60</v>
-      </c>
-      <c r="T22" t="s">
-        <v>61</v>
-      </c>
-      <c r="U22" t="s">
-        <v>30</v>
-      </c>
-      <c r="X22">
+        <v>37</v>
+      </c>
+      <c r="P22" t="s">
+        <v>68</v>
+      </c>
+      <c r="W22" t="s">
+        <v>34</v>
+      </c>
+      <c r="X22" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1346,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1358,33 +1460,36 @@
         <v>-48</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" t="s">
-        <v>37</v>
-      </c>
-      <c r="S23" t="s">
-        <v>45</v>
-      </c>
-      <c r="T23" t="s">
-        <v>59</v>
-      </c>
-      <c r="U23" t="s">
-        <v>30</v>
-      </c>
-      <c r="X23">
+        <v>37</v>
+      </c>
+      <c r="P23" t="s">
+        <v>71</v>
+      </c>
+      <c r="W23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X23" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1396,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1408,33 +1513,36 @@
         <v>48</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J24">
         <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="R24" t="s">
-        <v>37</v>
-      </c>
-      <c r="S24" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" t="s">
         <v>49</v>
       </c>
-      <c r="T24" t="s">
-        <v>62</v>
-      </c>
-      <c r="U24" t="s">
-        <v>37</v>
-      </c>
-      <c r="X24">
+      <c r="W24" t="s">
+        <v>42</v>
+      </c>
+      <c r="X24" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1446,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1458,33 +1566,36 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J25">
         <v>4</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" t="s">
-        <v>30</v>
-      </c>
-      <c r="S25" t="s">
-        <v>60</v>
-      </c>
-      <c r="T25" t="s">
-        <v>61</v>
-      </c>
-      <c r="U25" t="s">
-        <v>37</v>
-      </c>
-      <c r="X25">
+        <v>37</v>
+      </c>
+      <c r="P25" t="s">
+        <v>68</v>
+      </c>
+      <c r="W25" t="s">
+        <v>34</v>
+      </c>
+      <c r="X25" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1496,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1508,33 +1619,36 @@
         <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>48</v>
-      </c>
-      <c r="R26" t="s">
-        <v>37</v>
-      </c>
-      <c r="S26" t="s">
-        <v>60</v>
-      </c>
-      <c r="T26" t="s">
-        <v>61</v>
-      </c>
-      <c r="U26" t="s">
-        <v>37</v>
-      </c>
-      <c r="X26">
+        <v>56</v>
+      </c>
+      <c r="P26" t="s">
+        <v>68</v>
+      </c>
+      <c r="W26" t="s">
+        <v>42</v>
+      </c>
+      <c r="X26" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1546,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1558,33 +1672,36 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27">
         <v>-2</v>
       </c>
       <c r="K27" t="s">
-        <v>48</v>
-      </c>
-      <c r="R27" t="s">
-        <v>30</v>
-      </c>
-      <c r="S27" t="s">
+        <v>56</v>
+      </c>
+      <c r="P27" t="s">
         <v>49</v>
       </c>
-      <c r="T27" t="s">
-        <v>63</v>
-      </c>
-      <c r="U27" t="s">
-        <v>37</v>
-      </c>
-      <c r="X27">
+      <c r="W27" t="s">
+        <v>34</v>
+      </c>
+      <c r="X27" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1596,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1608,24 +1725,27 @@
         <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J28">
         <v>5</v>
       </c>
       <c r="K28" t="s">
-        <v>48</v>
-      </c>
-      <c r="R28" t="s">
-        <v>30</v>
-      </c>
-      <c r="S28" t="s">
-        <v>55</v>
-      </c>
-      <c r="X28">
+        <v>56</v>
+      </c>
+      <c r="P28" t="s">
+        <v>29</v>
+      </c>
+      <c r="W28" t="s">
+        <v>34</v>
+      </c>
+      <c r="X28" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1637,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1649,33 +1769,36 @@
         <v>37</v>
       </c>
       <c r="G29" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H29" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>48</v>
-      </c>
-      <c r="R29" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" t="s">
-        <v>55</v>
-      </c>
-      <c r="T29" t="s">
-        <v>59</v>
-      </c>
-      <c r="U29" t="s">
-        <v>37</v>
-      </c>
-      <c r="X29">
+        <v>56</v>
+      </c>
+      <c r="P29" t="s">
+        <v>29</v>
+      </c>
+      <c r="W29" t="s">
+        <v>34</v>
+      </c>
+      <c r="X29" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1687,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1699,33 +1822,36 @@
         <v>37</v>
       </c>
       <c r="G30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J30">
         <v>27</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S30" t="s">
+        <v>37</v>
+      </c>
+      <c r="P30" t="s">
         <v>49</v>
       </c>
-      <c r="T30" t="s">
-        <v>63</v>
-      </c>
-      <c r="U30" t="s">
-        <v>37</v>
-      </c>
-      <c r="X30">
+      <c r="W30" t="s">
+        <v>34</v>
+      </c>
+      <c r="X30" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1737,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1749,33 +1875,36 @@
         <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" t="s">
-        <v>30</v>
-      </c>
-      <c r="S31" t="s">
+        <v>37</v>
+      </c>
+      <c r="P31" t="s">
         <v>49</v>
       </c>
-      <c r="T31" t="s">
-        <v>66</v>
-      </c>
-      <c r="U31" t="s">
-        <v>30</v>
-      </c>
-      <c r="X31">
+      <c r="W31" t="s">
+        <v>34</v>
+      </c>
+      <c r="X31" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1787,21 +1916,21 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s">
-        <v>68</v>
-      </c>
-      <c r="X32">
+        <v>78</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -1813,19 +1942,19 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>-40</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I33" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -1836,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1848,30 +1977,33 @@
         <v>-20</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J34">
         <v>-2</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
-      </c>
-      <c r="R34" t="s">
-        <v>37</v>
-      </c>
-      <c r="S34" t="s">
-        <v>54</v>
-      </c>
-      <c r="U34" t="s">
-        <v>37</v>
-      </c>
-      <c r="X34">
+        <v>37</v>
+      </c>
+      <c r="P34" t="s">
+        <v>29</v>
+      </c>
+      <c r="W34" t="s">
+        <v>42</v>
+      </c>
+      <c r="X34" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1883,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1895,30 +2027,33 @@
         <v>-18</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J35">
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>48</v>
-      </c>
-      <c r="R35" t="s">
-        <v>37</v>
-      </c>
-      <c r="S35" t="s">
-        <v>54</v>
-      </c>
-      <c r="U35" t="s">
-        <v>30</v>
-      </c>
-      <c r="X35">
+        <v>56</v>
+      </c>
+      <c r="P35" t="s">
+        <v>29</v>
+      </c>
+      <c r="W35" t="s">
+        <v>42</v>
+      </c>
+      <c r="X35" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1930,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -1942,30 +2077,33 @@
         <v>-27</v>
       </c>
       <c r="G36" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>48</v>
-      </c>
-      <c r="R36" t="s">
-        <v>30</v>
-      </c>
-      <c r="S36" t="s">
-        <v>54</v>
-      </c>
-      <c r="U36" t="s">
-        <v>30</v>
-      </c>
-      <c r="X36">
+        <v>56</v>
+      </c>
+      <c r="P36" t="s">
+        <v>29</v>
+      </c>
+      <c r="W36" t="s">
+        <v>34</v>
+      </c>
+      <c r="X36" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -1977,7 +2115,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1989,27 +2127,30 @@
         <v>-31</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J37">
         <v>-25</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
-      </c>
-      <c r="R37" t="s">
-        <v>39</v>
-      </c>
-      <c r="U37" t="s">
-        <v>30</v>
-      </c>
-      <c r="X37">
+        <v>37</v>
+      </c>
+      <c r="P37" t="s">
+        <v>44</v>
+      </c>
+      <c r="W37" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -2021,7 +2162,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2033,27 +2174,30 @@
         <v>-6</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J38">
         <v>8</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
-      </c>
-      <c r="R38" t="s">
-        <v>39</v>
-      </c>
-      <c r="U38" t="s">
-        <v>37</v>
-      </c>
-      <c r="X38">
+        <v>37</v>
+      </c>
+      <c r="P38" t="s">
+        <v>44</v>
+      </c>
+      <c r="W38" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2065,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -2077,27 +2221,30 @@
         <v>-14</v>
       </c>
       <c r="G39" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
-      </c>
-      <c r="R39" t="s">
-        <v>39</v>
-      </c>
-      <c r="U39" t="s">
-        <v>30</v>
-      </c>
-      <c r="X39">
+        <v>37</v>
+      </c>
+      <c r="P39" t="s">
+        <v>44</v>
+      </c>
+      <c r="W39" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2109,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2121,15 +2268,15 @@
         <v>-14</v>
       </c>
       <c r="G40" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s">
-        <v>56</v>
-      </c>
-      <c r="X40">
+        <v>64</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2141,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2153,36 +2300,39 @@
         <v>-46</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J41">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="R41" t="s">
-        <v>37</v>
-      </c>
-      <c r="S41" t="s">
-        <v>45</v>
-      </c>
-      <c r="T41" t="s">
-        <v>71</v>
-      </c>
-      <c r="U41" t="s">
-        <v>30</v>
-      </c>
-      <c r="V41" t="s">
-        <v>37</v>
-      </c>
-      <c r="X41">
+        <v>37</v>
+      </c>
+      <c r="P41" t="s">
+        <v>52</v>
+      </c>
+      <c r="W41" t="s">
+        <v>42</v>
+      </c>
+      <c r="X41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2194,7 +2344,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2206,24 +2356,27 @@
         <v>47</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I42" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
-      </c>
-      <c r="R42" t="s">
-        <v>37</v>
-      </c>
-      <c r="S42" t="s">
-        <v>55</v>
-      </c>
-      <c r="X42">
+        <v>37</v>
+      </c>
+      <c r="P42" t="s">
+        <v>49</v>
+      </c>
+      <c r="W42" t="s">
+        <v>42</v>
+      </c>
+      <c r="X42" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2235,7 +2388,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2247,30 +2400,33 @@
         <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K43" t="s">
-        <v>48</v>
-      </c>
-      <c r="R43" t="s">
-        <v>37</v>
-      </c>
-      <c r="S43" t="s">
-        <v>55</v>
-      </c>
-      <c r="T43" t="s">
-        <v>59</v>
-      </c>
-      <c r="U43" t="s">
-        <v>37</v>
-      </c>
-      <c r="X43">
+        <v>56</v>
+      </c>
+      <c r="P43" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" t="s">
+        <v>42</v>
+      </c>
+      <c r="X43" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2282,7 +2438,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2294,30 +2450,33 @@
         <v>45</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J44">
         <v>11</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
-      </c>
-      <c r="R44" t="s">
-        <v>37</v>
-      </c>
-      <c r="S44" t="s">
-        <v>54</v>
-      </c>
-      <c r="U44" t="s">
-        <v>37</v>
-      </c>
-      <c r="X44">
+        <v>56</v>
+      </c>
+      <c r="P44" t="s">
+        <v>29</v>
+      </c>
+      <c r="W44" t="s">
+        <v>42</v>
+      </c>
+      <c r="X44" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB44">
         <v>4</v>
       </c>
     </row>
@@ -2329,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2341,30 +2500,33 @@
         <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J45">
         <v>-17</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
-      </c>
-      <c r="R45" t="s">
-        <v>30</v>
-      </c>
-      <c r="S45" t="s">
-        <v>54</v>
-      </c>
-      <c r="U45" t="s">
-        <v>37</v>
-      </c>
-      <c r="X45">
+        <v>37</v>
+      </c>
+      <c r="P45" t="s">
+        <v>49</v>
+      </c>
+      <c r="W45" t="s">
+        <v>34</v>
+      </c>
+      <c r="X45" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -2376,7 +2538,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2388,30 +2550,33 @@
         <v>-49</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J46">
         <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
-      </c>
-      <c r="R46" t="s">
-        <v>37</v>
-      </c>
-      <c r="S46" t="s">
-        <v>34</v>
-      </c>
-      <c r="U46" t="s">
-        <v>37</v>
-      </c>
-      <c r="X46">
+        <v>37</v>
+      </c>
+      <c r="P46" t="s">
+        <v>41</v>
+      </c>
+      <c r="W46" t="s">
+        <v>42</v>
+      </c>
+      <c r="X46" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2423,7 +2588,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2435,30 +2600,33 @@
         <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
-      </c>
-      <c r="R47" t="s">
-        <v>37</v>
-      </c>
-      <c r="S47" t="s">
-        <v>38</v>
-      </c>
-      <c r="U47" t="s">
-        <v>30</v>
-      </c>
-      <c r="X47">
+        <v>37</v>
+      </c>
+      <c r="P47" t="s">
+        <v>29</v>
+      </c>
+      <c r="W47" t="s">
+        <v>42</v>
+      </c>
+      <c r="X47" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -2470,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -2482,15 +2650,15 @@
         <v>46</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I48" t="s">
-        <v>56</v>
-      </c>
-      <c r="X48">
+        <v>64</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2502,7 +2670,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2514,33 +2682,36 @@
         <v>-19</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J49">
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>48</v>
-      </c>
-      <c r="R49" t="s">
-        <v>37</v>
-      </c>
-      <c r="S49" t="s">
-        <v>43</v>
-      </c>
-      <c r="T49" t="s">
-        <v>51</v>
-      </c>
-      <c r="U49" t="s">
-        <v>37</v>
-      </c>
-      <c r="X49">
+        <v>56</v>
+      </c>
+      <c r="P49" t="s">
+        <v>49</v>
+      </c>
+      <c r="W49" t="s">
+        <v>42</v>
+      </c>
+      <c r="X49" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2552,7 +2723,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2564,33 +2735,36 @@
         <v>-22</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>48</v>
-      </c>
-      <c r="R50" t="s">
-        <v>30</v>
-      </c>
-      <c r="S50" t="s">
-        <v>55</v>
-      </c>
-      <c r="T50" t="s">
-        <v>59</v>
-      </c>
-      <c r="U50" t="s">
-        <v>30</v>
-      </c>
-      <c r="X50">
+        <v>56</v>
+      </c>
+      <c r="P50" t="s">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>34</v>
+      </c>
+      <c r="X50" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2602,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2614,33 +2788,36 @@
         <v>-22</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J51">
         <v>43</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
-      </c>
-      <c r="R51" t="s">
-        <v>30</v>
-      </c>
-      <c r="S51" t="s">
-        <v>53</v>
-      </c>
-      <c r="T51" t="s">
-        <v>72</v>
-      </c>
-      <c r="U51" t="s">
-        <v>37</v>
-      </c>
-      <c r="X51">
+        <v>37</v>
+      </c>
+      <c r="P51" t="s">
+        <v>29</v>
+      </c>
+      <c r="W51" t="s">
+        <v>34</v>
+      </c>
+      <c r="X51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB51">
         <v>4</v>
       </c>
     </row>
@@ -2652,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2664,33 +2841,36 @@
         <v>35</v>
       </c>
       <c r="G52" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I52" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J52">
         <v>6</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
-      </c>
-      <c r="R52" t="s">
-        <v>30</v>
-      </c>
-      <c r="S52" t="s">
-        <v>43</v>
-      </c>
-      <c r="T52" t="s">
-        <v>59</v>
-      </c>
-      <c r="U52" t="s">
-        <v>37</v>
-      </c>
-      <c r="X52">
+        <v>37</v>
+      </c>
+      <c r="P52" t="s">
+        <v>49</v>
+      </c>
+      <c r="W52" t="s">
+        <v>34</v>
+      </c>
+      <c r="X52" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2702,7 +2882,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -2714,33 +2894,36 @@
         <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J53">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
-      </c>
-      <c r="R53" t="s">
-        <v>30</v>
-      </c>
-      <c r="S53" t="s">
+        <v>37</v>
+      </c>
+      <c r="P53" t="s">
         <v>49</v>
       </c>
-      <c r="T53" t="s">
-        <v>73</v>
-      </c>
-      <c r="U53" t="s">
-        <v>37</v>
-      </c>
-      <c r="X53">
+      <c r="W53" t="s">
+        <v>34</v>
+      </c>
+      <c r="X53" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -2752,7 +2935,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2764,33 +2947,36 @@
         <v>22</v>
       </c>
       <c r="G54" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J54">
         <v>11</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
-      </c>
-      <c r="R54" t="s">
-        <v>30</v>
-      </c>
-      <c r="S54" t="s">
-        <v>49</v>
-      </c>
-      <c r="T54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U54" t="s">
-        <v>37</v>
-      </c>
-      <c r="X54">
+        <v>37</v>
+      </c>
+      <c r="P54" t="s">
+        <v>29</v>
+      </c>
+      <c r="W54" t="s">
+        <v>34</v>
+      </c>
+      <c r="X54" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2802,7 +2988,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2814,33 +3000,36 @@
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J55">
         <v>11</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
-      </c>
-      <c r="R55" t="s">
-        <v>30</v>
-      </c>
-      <c r="S55" t="s">
-        <v>55</v>
-      </c>
-      <c r="T55" t="s">
-        <v>59</v>
-      </c>
-      <c r="U55" t="s">
-        <v>30</v>
-      </c>
-      <c r="X55">
+        <v>37</v>
+      </c>
+      <c r="P55" t="s">
+        <v>49</v>
+      </c>
+      <c r="W55" t="s">
+        <v>34</v>
+      </c>
+      <c r="X55" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -2852,21 +3041,21 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I56" t="s">
-        <v>68</v>
-      </c>
-      <c r="X56">
+        <v>78</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -2878,19 +3067,19 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>-40</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I57" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -2901,7 +3090,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2913,30 +3102,33 @@
         <v>-16</v>
       </c>
       <c r="G58" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H58" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J58">
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
-      </c>
-      <c r="R58" t="s">
-        <v>30</v>
-      </c>
-      <c r="S58" t="s">
-        <v>54</v>
-      </c>
-      <c r="U58" t="s">
-        <v>37</v>
-      </c>
-      <c r="X58">
+        <v>37</v>
+      </c>
+      <c r="P58" t="s">
+        <v>29</v>
+      </c>
+      <c r="W58" t="s">
+        <v>34</v>
+      </c>
+      <c r="X58" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB58">
         <v>5</v>
       </c>
     </row>
@@ -2948,7 +3140,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -2960,30 +3152,33 @@
         <v>-18</v>
       </c>
       <c r="G59" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J59">
         <v>-2</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
-      </c>
-      <c r="R59" t="s">
-        <v>30</v>
-      </c>
-      <c r="S59" t="s">
-        <v>54</v>
-      </c>
-      <c r="U59" t="s">
-        <v>37</v>
-      </c>
-      <c r="X59">
+        <v>37</v>
+      </c>
+      <c r="P59" t="s">
+        <v>41</v>
+      </c>
+      <c r="W59" t="s">
+        <v>34</v>
+      </c>
+      <c r="X59" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -2995,7 +3190,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -3007,27 +3202,30 @@
         <v>-16</v>
       </c>
       <c r="G60" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
-      </c>
-      <c r="R60" t="s">
-        <v>39</v>
-      </c>
-      <c r="U60" t="s">
-        <v>30</v>
-      </c>
-      <c r="X60">
+        <v>37</v>
+      </c>
+      <c r="P60" t="s">
+        <v>41</v>
+      </c>
+      <c r="W60" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB60">
         <v>5</v>
       </c>
     </row>
@@ -3039,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -3051,15 +3249,15 @@
         <v>-16</v>
       </c>
       <c r="G61" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H61" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>56</v>
-      </c>
-      <c r="X61">
+        <v>64</v>
+      </c>
+      <c r="AB61">
         <v>5</v>
       </c>
     </row>
@@ -3071,7 +3269,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3083,33 +3281,36 @@
         <v>-46</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J62">
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>33</v>
-      </c>
-      <c r="R62" t="s">
-        <v>37</v>
-      </c>
-      <c r="S62" t="s">
-        <v>74</v>
-      </c>
-      <c r="T62" t="s">
-        <v>75</v>
-      </c>
-      <c r="U62" t="s">
-        <v>37</v>
-      </c>
-      <c r="X62">
+        <v>37</v>
+      </c>
+      <c r="P62" t="s">
+        <v>29</v>
+      </c>
+      <c r="W62" t="s">
+        <v>42</v>
+      </c>
+      <c r="X62" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -3121,7 +3322,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3133,24 +3334,27 @@
         <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J63">
         <v>-5</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
-      </c>
-      <c r="R63" t="s">
-        <v>30</v>
-      </c>
-      <c r="S63" t="s">
-        <v>74</v>
-      </c>
-      <c r="X63">
+        <v>56</v>
+      </c>
+      <c r="P63" t="s">
+        <v>49</v>
+      </c>
+      <c r="W63" t="s">
+        <v>34</v>
+      </c>
+      <c r="X63" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB63">
         <v>5</v>
       </c>
     </row>
@@ -3162,7 +3366,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3174,33 +3378,36 @@
         <v>44</v>
       </c>
       <c r="G64" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J64">
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
-      </c>
-      <c r="R64" t="s">
-        <v>30</v>
-      </c>
-      <c r="S64" t="s">
-        <v>74</v>
-      </c>
-      <c r="T64" t="s">
-        <v>76</v>
-      </c>
-      <c r="U64" t="s">
-        <v>30</v>
-      </c>
-      <c r="X64">
+        <v>37</v>
+      </c>
+      <c r="P64" t="s">
+        <v>49</v>
+      </c>
+      <c r="W64" t="s">
+        <v>34</v>
+      </c>
+      <c r="X64" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3212,7 +3419,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3224,33 +3431,36 @@
         <v>37</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I65" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J65">
         <v>10</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
-      </c>
-      <c r="R65" t="s">
-        <v>37</v>
-      </c>
-      <c r="S65" t="s">
+        <v>37</v>
+      </c>
+      <c r="P65" t="s">
         <v>49</v>
       </c>
-      <c r="T65" t="s">
-        <v>51</v>
-      </c>
-      <c r="U65" t="s">
-        <v>37</v>
-      </c>
-      <c r="X65">
+      <c r="W65" t="s">
+        <v>42</v>
+      </c>
+      <c r="X65" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3262,7 +3472,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3274,33 +3484,36 @@
         <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>48</v>
-      </c>
-      <c r="R66" t="s">
-        <v>30</v>
-      </c>
-      <c r="S66" t="s">
-        <v>74</v>
-      </c>
-      <c r="T66" t="s">
-        <v>58</v>
-      </c>
-      <c r="U66" t="s">
-        <v>30</v>
-      </c>
-      <c r="X66">
+        <v>56</v>
+      </c>
+      <c r="P66" t="s">
+        <v>49</v>
+      </c>
+      <c r="W66" t="s">
+        <v>34</v>
+      </c>
+      <c r="X66" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3312,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3324,33 +3537,36 @@
         <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H67" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I67" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>48</v>
-      </c>
-      <c r="R67" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" t="s">
-        <v>55</v>
-      </c>
-      <c r="T67" t="s">
-        <v>50</v>
-      </c>
-      <c r="U67" t="s">
-        <v>30</v>
-      </c>
-      <c r="X67">
+        <v>56</v>
+      </c>
+      <c r="P67" t="s">
+        <v>49</v>
+      </c>
+      <c r="W67" t="s">
+        <v>42</v>
+      </c>
+      <c r="X67" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3362,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -3374,21 +3590,24 @@
         <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I68" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>48</v>
-      </c>
-      <c r="S68" t="s">
-        <v>60</v>
-      </c>
-      <c r="X68">
+        <v>56</v>
+      </c>
+      <c r="P68" t="s">
+        <v>68</v>
+      </c>
+      <c r="X68" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3400,7 +3619,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -3412,33 +3631,36 @@
         <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I69" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>48</v>
-      </c>
-      <c r="R69" t="s">
-        <v>30</v>
-      </c>
-      <c r="S69" t="s">
-        <v>60</v>
-      </c>
-      <c r="T69" t="s">
-        <v>63</v>
-      </c>
-      <c r="U69" t="s">
-        <v>30</v>
-      </c>
-      <c r="X69">
+        <v>56</v>
+      </c>
+      <c r="P69" t="s">
+        <v>68</v>
+      </c>
+      <c r="W69" t="s">
+        <v>34</v>
+      </c>
+      <c r="X69" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3450,7 +3672,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -3462,15 +3684,15 @@
         <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H70" t="s">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s">
         <v>78</v>
       </c>
-      <c r="I70" t="s">
-        <v>68</v>
-      </c>
-      <c r="X70">
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3482,19 +3704,19 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F71">
         <v>-40</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I71" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
@@ -3505,7 +3727,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3517,30 +3739,33 @@
         <v>-27</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H72" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J72">
         <v>5</v>
       </c>
       <c r="K72" t="s">
-        <v>48</v>
-      </c>
-      <c r="R72" t="s">
-        <v>39</v>
-      </c>
-      <c r="S72" t="s">
-        <v>55</v>
-      </c>
-      <c r="U72" t="s">
-        <v>30</v>
-      </c>
-      <c r="X72">
+        <v>56</v>
+      </c>
+      <c r="P72" t="s">
+        <v>44</v>
+      </c>
+      <c r="W72" t="s">
+        <v>45</v>
+      </c>
+      <c r="X72" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB72">
         <v>6</v>
       </c>
     </row>
@@ -3552,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3564,30 +3789,33 @@
         <v>-32</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
-      </c>
-      <c r="R73" t="s">
-        <v>37</v>
-      </c>
-      <c r="S73" t="s">
-        <v>54</v>
-      </c>
-      <c r="U73" t="s">
-        <v>30</v>
-      </c>
-      <c r="X73">
+        <v>37</v>
+      </c>
+      <c r="P73" t="s">
+        <v>29</v>
+      </c>
+      <c r="W73" t="s">
+        <v>42</v>
+      </c>
+      <c r="X73" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB73">
         <v>6</v>
       </c>
     </row>
@@ -3599,21 +3827,21 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F74">
         <v>-40</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I74" t="s">
-        <v>28</v>
-      </c>
-      <c r="X74">
+        <v>32</v>
+      </c>
+      <c r="AB74">
         <v>6</v>
       </c>
     </row>
@@ -3625,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3637,33 +3865,36 @@
         <v>-32</v>
       </c>
       <c r="G75" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J75">
         <v>9</v>
       </c>
       <c r="K75" t="s">
-        <v>33</v>
-      </c>
-      <c r="R75" t="s">
-        <v>37</v>
-      </c>
-      <c r="S75" t="s">
-        <v>43</v>
-      </c>
-      <c r="T75" t="s">
-        <v>80</v>
-      </c>
-      <c r="U75" t="s">
-        <v>37</v>
-      </c>
-      <c r="X75">
+        <v>37</v>
+      </c>
+      <c r="P75" t="s">
+        <v>41</v>
+      </c>
+      <c r="W75" t="s">
+        <v>42</v>
+      </c>
+      <c r="X75" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3675,7 +3906,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3687,24 +3918,27 @@
         <v>-41</v>
       </c>
       <c r="G76" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J76">
         <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>33</v>
-      </c>
-      <c r="R76" t="s">
-        <v>37</v>
-      </c>
-      <c r="S76" t="s">
-        <v>43</v>
-      </c>
-      <c r="X76">
+        <v>37</v>
+      </c>
+      <c r="P76" t="s">
+        <v>29</v>
+      </c>
+      <c r="W76" t="s">
+        <v>42</v>
+      </c>
+      <c r="X76" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -3716,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3728,33 +3962,36 @@
         <v>-46</v>
       </c>
       <c r="G77" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I77" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
-      </c>
-      <c r="R77" t="s">
-        <v>37</v>
-      </c>
-      <c r="S77" t="s">
-        <v>43</v>
-      </c>
-      <c r="T77" t="s">
+        <v>56</v>
+      </c>
+      <c r="P77" t="s">
+        <v>29</v>
+      </c>
+      <c r="W77" t="s">
+        <v>42</v>
+      </c>
+      <c r="X77" t="s">
         <v>50</v>
       </c>
-      <c r="U77" t="s">
-        <v>37</v>
-      </c>
-      <c r="X77">
+      <c r="Y77" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -3766,7 +4003,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3778,36 +4015,39 @@
         <v>-46</v>
       </c>
       <c r="G78" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J78">
         <v>-10</v>
       </c>
       <c r="K78" t="s">
-        <v>48</v>
-      </c>
-      <c r="R78" t="s">
-        <v>30</v>
-      </c>
-      <c r="S78" t="s">
-        <v>45</v>
-      </c>
-      <c r="T78" t="s">
-        <v>46</v>
-      </c>
-      <c r="U78" t="s">
-        <v>30</v>
-      </c>
-      <c r="V78" t="s">
-        <v>37</v>
-      </c>
-      <c r="X78">
+        <v>56</v>
+      </c>
+      <c r="P78" t="s">
+        <v>52</v>
+      </c>
+      <c r="W78" t="s">
+        <v>34</v>
+      </c>
+      <c r="X78" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -3819,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3831,33 +4071,36 @@
         <v>-36</v>
       </c>
       <c r="G79" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I79" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J79">
         <v>12</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
-      </c>
-      <c r="R79" t="s">
-        <v>30</v>
-      </c>
-      <c r="S79" t="s">
-        <v>74</v>
-      </c>
-      <c r="T79" t="s">
-        <v>81</v>
-      </c>
-      <c r="U79" t="s">
-        <v>37</v>
-      </c>
-      <c r="X79">
+        <v>37</v>
+      </c>
+      <c r="P79" t="s">
+        <v>49</v>
+      </c>
+      <c r="W79" t="s">
+        <v>34</v>
+      </c>
+      <c r="X79" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -3869,7 +4112,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -3881,18 +4124,18 @@
         <v>-48</v>
       </c>
       <c r="G80" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>48</v>
-      </c>
-      <c r="X80">
+        <v>56</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -3904,7 +4147,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3916,36 +4159,39 @@
         <v>-48</v>
       </c>
       <c r="G81" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I81" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>48</v>
-      </c>
-      <c r="R81" t="s">
-        <v>30</v>
-      </c>
-      <c r="S81" t="s">
-        <v>82</v>
-      </c>
-      <c r="T81" t="s">
-        <v>66</v>
-      </c>
-      <c r="U81" t="s">
-        <v>37</v>
-      </c>
-      <c r="V81" t="s">
-        <v>30</v>
-      </c>
-      <c r="X81">
+        <v>56</v>
+      </c>
+      <c r="P81" t="s">
+        <v>29</v>
+      </c>
+      <c r="W81" t="s">
+        <v>34</v>
+      </c>
+      <c r="X81" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -3957,7 +4203,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -3969,15 +4215,15 @@
         <v>-48</v>
       </c>
       <c r="G82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H82" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I82" t="s">
-        <v>56</v>
-      </c>
-      <c r="X82">
+        <v>64</v>
+      </c>
+      <c r="AB82">
         <v>5</v>
       </c>
     </row>
@@ -3989,7 +4235,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4001,30 +4247,33 @@
         <v>-41</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H83" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
-      </c>
-      <c r="R83" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" t="s">
-        <v>83</v>
-      </c>
-      <c r="U83" t="s">
-        <v>37</v>
-      </c>
-      <c r="X83">
+        <v>37</v>
+      </c>
+      <c r="P83" t="s">
+        <v>29</v>
+      </c>
+      <c r="W83" t="s">
+        <v>34</v>
+      </c>
+      <c r="X83" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB83">
         <v>7</v>
       </c>
     </row>
@@ -4036,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4048,27 +4297,30 @@
         <v>-41</v>
       </c>
       <c r="G84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J84">
         <v>-17</v>
       </c>
       <c r="K84" t="s">
-        <v>33</v>
-      </c>
-      <c r="R84" t="s">
-        <v>39</v>
-      </c>
-      <c r="U84" t="s">
-        <v>30</v>
-      </c>
-      <c r="X84">
+        <v>37</v>
+      </c>
+      <c r="P84" t="s">
+        <v>41</v>
+      </c>
+      <c r="W84" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB84">
         <v>7</v>
       </c>
     </row>
@@ -4080,7 +4332,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -4092,24 +4344,27 @@
         <v>-24</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I85" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J85">
         <v>-5</v>
       </c>
       <c r="K85" t="s">
-        <v>33</v>
-      </c>
-      <c r="R85" t="s">
-        <v>37</v>
-      </c>
-      <c r="S85" t="s">
-        <v>34</v>
-      </c>
-      <c r="X85">
+        <v>37</v>
+      </c>
+      <c r="P85" t="s">
+        <v>29</v>
+      </c>
+      <c r="W85" t="s">
+        <v>42</v>
+      </c>
+      <c r="X85" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB85">
         <v>7</v>
       </c>
     </row>
@@ -4121,7 +4376,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -4133,30 +4388,33 @@
         <v>-19</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I86" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J86">
         <v>10</v>
       </c>
       <c r="K86" t="s">
-        <v>33</v>
-      </c>
-      <c r="R86" t="s">
-        <v>37</v>
-      </c>
-      <c r="S86" t="s">
-        <v>34</v>
-      </c>
-      <c r="U86" t="s">
-        <v>30</v>
-      </c>
-      <c r="X86">
+        <v>37</v>
+      </c>
+      <c r="P86" t="s">
+        <v>29</v>
+      </c>
+      <c r="W86" t="s">
+        <v>42</v>
+      </c>
+      <c r="X86" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB86">
         <v>7</v>
       </c>
     </row>
@@ -4168,7 +4426,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -4180,15 +4438,15 @@
         <v>-29</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H87" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>56</v>
-      </c>
-      <c r="X87">
+        <v>64</v>
+      </c>
+      <c r="AB87">
         <v>7</v>
       </c>
     </row>
@@ -4200,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4212,33 +4470,36 @@
         <v>-38</v>
       </c>
       <c r="G88" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J88">
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>48</v>
-      </c>
-      <c r="R88" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" t="s">
+        <v>56</v>
+      </c>
+      <c r="P88" t="s">
         <v>49</v>
       </c>
-      <c r="T88" t="s">
-        <v>73</v>
-      </c>
-      <c r="U88" t="s">
-        <v>37</v>
-      </c>
-      <c r="X88">
+      <c r="W88" t="s">
+        <v>34</v>
+      </c>
+      <c r="X88" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB88">
         <v>6</v>
       </c>
     </row>
@@ -4250,7 +4511,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4262,33 +4523,36 @@
         <v>-40</v>
       </c>
       <c r="G89" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J89">
         <v>-2</v>
       </c>
       <c r="K89" t="s">
-        <v>48</v>
-      </c>
-      <c r="R89" t="s">
-        <v>30</v>
-      </c>
-      <c r="S89" t="s">
-        <v>82</v>
-      </c>
-      <c r="T89" t="s">
-        <v>80</v>
-      </c>
-      <c r="U89" t="s">
-        <v>30</v>
-      </c>
-      <c r="X89">
+        <v>56</v>
+      </c>
+      <c r="P89" t="s">
+        <v>41</v>
+      </c>
+      <c r="W89" t="s">
+        <v>34</v>
+      </c>
+      <c r="X89" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB89">
         <v>6</v>
       </c>
     </row>
@@ -4300,7 +4564,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4312,33 +4576,36 @@
         <v>-38</v>
       </c>
       <c r="G90" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I90" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>48</v>
-      </c>
-      <c r="R90" t="s">
-        <v>30</v>
-      </c>
-      <c r="S90" t="s">
+        <v>56</v>
+      </c>
+      <c r="P90" t="s">
         <v>49</v>
       </c>
-      <c r="T90" t="s">
-        <v>63</v>
-      </c>
-      <c r="U90" t="s">
-        <v>30</v>
-      </c>
-      <c r="X90">
+      <c r="W90" t="s">
+        <v>34</v>
+      </c>
+      <c r="X90" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB90">
         <v>6</v>
       </c>
     </row>
@@ -4350,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>4</v>
@@ -4362,15 +4629,15 @@
         <v>-38</v>
       </c>
       <c r="G91" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H91" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I91" t="s">
-        <v>56</v>
-      </c>
-      <c r="X91">
+        <v>64</v>
+      </c>
+      <c r="AB91">
         <v>6</v>
       </c>
     </row>
@@ -4382,7 +4649,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4394,30 +4661,33 @@
         <v>-41</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J92">
         <v>6</v>
       </c>
       <c r="K92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R92" t="s">
-        <v>39</v>
-      </c>
-      <c r="S92" t="s">
-        <v>55</v>
-      </c>
-      <c r="U92" t="s">
-        <v>30</v>
-      </c>
-      <c r="X92">
+        <v>56</v>
+      </c>
+      <c r="P92" t="s">
+        <v>44</v>
+      </c>
+      <c r="W92" t="s">
+        <v>45</v>
+      </c>
+      <c r="X92" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB92">
         <v>8</v>
       </c>
     </row>
@@ -4429,7 +4699,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -4441,30 +4711,33 @@
         <v>-47</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>33</v>
-      </c>
-      <c r="R93" t="s">
-        <v>39</v>
-      </c>
-      <c r="S93" t="s">
-        <v>55</v>
-      </c>
-      <c r="U93" t="s">
-        <v>30</v>
-      </c>
-      <c r="X93">
+        <v>37</v>
+      </c>
+      <c r="P93" t="s">
+        <v>44</v>
+      </c>
+      <c r="W93" t="s">
+        <v>45</v>
+      </c>
+      <c r="X93" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB93">
         <v>8</v>
       </c>
     </row>
@@ -4476,7 +4749,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -4488,30 +4761,33 @@
         <v>-47</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I94" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J94">
         <v>11</v>
       </c>
       <c r="K94" t="s">
-        <v>48</v>
-      </c>
-      <c r="R94" t="s">
-        <v>39</v>
-      </c>
-      <c r="S94" t="s">
-        <v>55</v>
-      </c>
-      <c r="U94" t="s">
-        <v>37</v>
-      </c>
-      <c r="X94">
+        <v>56</v>
+      </c>
+      <c r="P94" t="s">
+        <v>44</v>
+      </c>
+      <c r="W94" t="s">
+        <v>45</v>
+      </c>
+      <c r="X94" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB94">
         <v>8</v>
       </c>
     </row>
@@ -4523,7 +4799,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4535,30 +4811,33 @@
         <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I95" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>33</v>
-      </c>
-      <c r="R95" t="s">
-        <v>39</v>
-      </c>
-      <c r="S95" t="s">
-        <v>55</v>
-      </c>
-      <c r="U95" t="s">
-        <v>30</v>
-      </c>
-      <c r="X95">
+        <v>37</v>
+      </c>
+      <c r="P95" t="s">
+        <v>44</v>
+      </c>
+      <c r="W95" t="s">
+        <v>45</v>
+      </c>
+      <c r="X95" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95">
         <v>8</v>
       </c>
     </row>
@@ -4570,7 +4849,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -4582,18 +4861,18 @@
         <v>42</v>
       </c>
       <c r="G96" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>33</v>
-      </c>
-      <c r="X96">
+        <v>37</v>
+      </c>
+      <c r="AB96">
         <v>8</v>
       </c>
     </row>
@@ -4605,7 +4884,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -4617,30 +4896,33 @@
         <v>42</v>
       </c>
       <c r="G97" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H97" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I97" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J97">
         <v>21</v>
       </c>
       <c r="K97" t="s">
-        <v>48</v>
-      </c>
-      <c r="R97" t="s">
-        <v>37</v>
-      </c>
-      <c r="S97" t="s">
-        <v>84</v>
-      </c>
-      <c r="U97" t="s">
-        <v>37</v>
-      </c>
-      <c r="X97">
+        <v>56</v>
+      </c>
+      <c r="P97" t="s">
+        <v>29</v>
+      </c>
+      <c r="W97" t="s">
+        <v>42</v>
+      </c>
+      <c r="X97" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB97">
         <v>8</v>
       </c>
     </row>
@@ -4652,7 +4934,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4664,30 +4946,33 @@
         <v>21</v>
       </c>
       <c r="G98" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H98" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I98" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>33</v>
-      </c>
-      <c r="R98" t="s">
-        <v>39</v>
-      </c>
-      <c r="S98" t="s">
-        <v>55</v>
-      </c>
-      <c r="U98" t="s">
-        <v>30</v>
-      </c>
-      <c r="X98">
+        <v>37</v>
+      </c>
+      <c r="P98" t="s">
+        <v>44</v>
+      </c>
+      <c r="W98" t="s">
+        <v>45</v>
+      </c>
+      <c r="X98" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB98">
         <v>8</v>
       </c>
     </row>
@@ -4699,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -4711,30 +4996,33 @@
         <v>21</v>
       </c>
       <c r="G99" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I99" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>33</v>
-      </c>
-      <c r="R99" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" t="s">
-        <v>38</v>
-      </c>
-      <c r="U99" t="s">
-        <v>37</v>
-      </c>
-      <c r="X99">
+        <v>37</v>
+      </c>
+      <c r="P99" t="s">
+        <v>49</v>
+      </c>
+      <c r="W99" t="s">
+        <v>34</v>
+      </c>
+      <c r="X99" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB99">
         <v>8</v>
       </c>
     </row>
@@ -4746,7 +5034,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -4758,30 +5046,33 @@
         <v>21</v>
       </c>
       <c r="G100" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H100" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I100" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J100">
         <v>-1</v>
       </c>
       <c r="K100" t="s">
-        <v>33</v>
-      </c>
-      <c r="R100" t="s">
-        <v>37</v>
-      </c>
-      <c r="S100" t="s">
-        <v>54</v>
-      </c>
-      <c r="U100" t="s">
-        <v>37</v>
-      </c>
-      <c r="X100">
+        <v>37</v>
+      </c>
+      <c r="P100" t="s">
+        <v>49</v>
+      </c>
+      <c r="W100" t="s">
+        <v>42</v>
+      </c>
+      <c r="X100" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB100">
         <v>8</v>
       </c>
     </row>
@@ -4793,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -4805,30 +5096,33 @@
         <v>22</v>
       </c>
       <c r="G101" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H101" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I101" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>33</v>
-      </c>
-      <c r="R101" t="s">
-        <v>37</v>
-      </c>
-      <c r="S101" t="s">
-        <v>38</v>
-      </c>
-      <c r="U101" t="s">
-        <v>30</v>
-      </c>
-      <c r="X101">
+        <v>37</v>
+      </c>
+      <c r="P101" t="s">
+        <v>49</v>
+      </c>
+      <c r="W101" t="s">
+        <v>42</v>
+      </c>
+      <c r="X101" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB101">
         <v>8</v>
       </c>
     </row>
@@ -4840,7 +5134,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4852,33 +5146,36 @@
         <v>-22</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J102">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>48</v>
-      </c>
-      <c r="R102" t="s">
-        <v>37</v>
-      </c>
-      <c r="S102" t="s">
-        <v>74</v>
-      </c>
-      <c r="T102" t="s">
-        <v>80</v>
-      </c>
-      <c r="U102" t="s">
-        <v>30</v>
-      </c>
-      <c r="X102">
+        <v>56</v>
+      </c>
+      <c r="P102" t="s">
+        <v>49</v>
+      </c>
+      <c r="W102" t="s">
+        <v>42</v>
+      </c>
+      <c r="X102" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102">
         <v>7</v>
       </c>
     </row>
@@ -4890,7 +5187,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -4902,33 +5199,36 @@
         <v>-23</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I103" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J103">
         <v>12</v>
       </c>
       <c r="K103" t="s">
-        <v>33</v>
-      </c>
-      <c r="R103" t="s">
-        <v>37</v>
-      </c>
-      <c r="S103" t="s">
-        <v>55</v>
-      </c>
-      <c r="T103" t="s">
-        <v>85</v>
-      </c>
-      <c r="U103" t="s">
-        <v>30</v>
-      </c>
-      <c r="X103">
+        <v>37</v>
+      </c>
+      <c r="P103" t="s">
+        <v>29</v>
+      </c>
+      <c r="W103" t="s">
+        <v>42</v>
+      </c>
+      <c r="X103" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB103">
         <v>7</v>
       </c>
     </row>
@@ -4940,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4952,33 +5252,36 @@
         <v>-35</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I104" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J104">
         <v>23</v>
       </c>
       <c r="K104" t="s">
-        <v>33</v>
-      </c>
-      <c r="R104" t="s">
-        <v>37</v>
-      </c>
-      <c r="S104" t="s">
+        <v>37</v>
+      </c>
+      <c r="P104" t="s">
         <v>49</v>
       </c>
-      <c r="T104" t="s">
-        <v>63</v>
-      </c>
-      <c r="U104" t="s">
-        <v>30</v>
-      </c>
-      <c r="X104">
+      <c r="W104" t="s">
+        <v>42</v>
+      </c>
+      <c r="X104" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB104">
         <v>7</v>
       </c>
     </row>
@@ -4990,7 +5293,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -5002,33 +5305,36 @@
         <v>42</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J105">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>48</v>
-      </c>
-      <c r="R105" t="s">
-        <v>30</v>
-      </c>
-      <c r="S105" t="s">
-        <v>43</v>
-      </c>
-      <c r="T105" t="s">
-        <v>80</v>
-      </c>
-      <c r="U105" t="s">
-        <v>30</v>
-      </c>
-      <c r="X105">
+        <v>56</v>
+      </c>
+      <c r="P105" t="s">
+        <v>29</v>
+      </c>
+      <c r="W105" t="s">
+        <v>34</v>
+      </c>
+      <c r="X105" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB105">
         <v>7</v>
       </c>
     </row>
@@ -5040,7 +5346,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5052,33 +5358,36 @@
         <v>41</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J106">
         <v>9</v>
       </c>
       <c r="K106" t="s">
-        <v>33</v>
-      </c>
-      <c r="R106" t="s">
-        <v>37</v>
-      </c>
-      <c r="S106" t="s">
+        <v>37</v>
+      </c>
+      <c r="P106" t="s">
         <v>49</v>
       </c>
-      <c r="T106" t="s">
-        <v>58</v>
-      </c>
-      <c r="U106" t="s">
-        <v>37</v>
-      </c>
-      <c r="X106">
+      <c r="W106" t="s">
+        <v>42</v>
+      </c>
+      <c r="X106" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB106">
         <v>7</v>
       </c>
     </row>
@@ -5090,7 +5399,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5102,33 +5411,36 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>-5</v>
       </c>
       <c r="K107" t="s">
-        <v>48</v>
-      </c>
-      <c r="R107" t="s">
-        <v>37</v>
-      </c>
-      <c r="S107" t="s">
-        <v>49</v>
-      </c>
-      <c r="T107" t="s">
-        <v>86</v>
-      </c>
-      <c r="U107" t="s">
-        <v>37</v>
-      </c>
-      <c r="X107">
+        <v>56</v>
+      </c>
+      <c r="P107" t="s">
+        <v>29</v>
+      </c>
+      <c r="W107" t="s">
+        <v>42</v>
+      </c>
+      <c r="X107" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB107">
         <v>7</v>
       </c>
     </row>
@@ -5140,7 +5452,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -5152,18 +5464,18 @@
         <v>37</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I108" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>48</v>
-      </c>
-      <c r="X108">
+        <v>56</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -5175,7 +5487,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5187,33 +5499,36 @@
         <v>37</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I109" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>48</v>
-      </c>
-      <c r="R109" t="s">
-        <v>30</v>
-      </c>
-      <c r="S109" t="s">
-        <v>43</v>
-      </c>
-      <c r="T109" t="s">
-        <v>63</v>
-      </c>
-      <c r="U109" t="s">
-        <v>37</v>
-      </c>
-      <c r="X109">
+        <v>56</v>
+      </c>
+      <c r="P109" t="s">
+        <v>29</v>
+      </c>
+      <c r="W109" t="s">
+        <v>34</v>
+      </c>
+      <c r="X109" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB109">
         <v>7</v>
       </c>
     </row>
@@ -5225,7 +5540,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5237,33 +5552,36 @@
         <v>37</v>
       </c>
       <c r="G110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H110" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I110" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J110">
         <v>12</v>
       </c>
       <c r="K110" t="s">
-        <v>48</v>
-      </c>
-      <c r="R110" t="s">
-        <v>30</v>
-      </c>
-      <c r="S110" t="s">
+        <v>56</v>
+      </c>
+      <c r="P110" t="s">
         <v>49</v>
       </c>
-      <c r="T110" t="s">
-        <v>87</v>
-      </c>
-      <c r="U110" t="s">
-        <v>30</v>
-      </c>
-      <c r="X110">
+      <c r="W110" t="s">
+        <v>34</v>
+      </c>
+      <c r="X110" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB110">
         <v>7</v>
       </c>
     </row>
@@ -5275,7 +5593,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -5287,33 +5605,36 @@
         <v>25</v>
       </c>
       <c r="G111" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H111" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I111" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>48</v>
-      </c>
-      <c r="R111" t="s">
-        <v>37</v>
-      </c>
-      <c r="S111" t="s">
+        <v>56</v>
+      </c>
+      <c r="P111" t="s">
         <v>49</v>
       </c>
-      <c r="T111" t="s">
-        <v>76</v>
-      </c>
-      <c r="U111" t="s">
-        <v>30</v>
-      </c>
-      <c r="X111">
+      <c r="W111" t="s">
+        <v>42</v>
+      </c>
+      <c r="X111" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB111">
         <v>7</v>
       </c>
     </row>
@@ -5325,7 +5646,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5337,27 +5658,30 @@
         <v>-25</v>
       </c>
       <c r="G112" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H112" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I112" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J112">
         <v>5</v>
       </c>
       <c r="K112" t="s">
-        <v>48</v>
-      </c>
-      <c r="R112" t="s">
-        <v>30</v>
-      </c>
-      <c r="U112" t="s">
-        <v>30</v>
-      </c>
-      <c r="X112">
+        <v>56</v>
+      </c>
+      <c r="P112" t="s">
+        <v>41</v>
+      </c>
+      <c r="W112" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB112">
         <v>9</v>
       </c>
     </row>
@@ -5369,7 +5693,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5381,30 +5705,33 @@
         <v>-30</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H113" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I113" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>33</v>
-      </c>
-      <c r="R113" t="s">
-        <v>39</v>
-      </c>
-      <c r="S113" t="s">
-        <v>55</v>
-      </c>
-      <c r="U113" t="s">
-        <v>37</v>
-      </c>
-      <c r="X113">
+        <v>37</v>
+      </c>
+      <c r="P113" t="s">
+        <v>44</v>
+      </c>
+      <c r="W113" t="s">
+        <v>45</v>
+      </c>
+      <c r="X113" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB113">
         <v>9</v>
       </c>
     </row>
@@ -5416,7 +5743,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5428,30 +5755,33 @@
         <v>-30</v>
       </c>
       <c r="G114" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H114" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I114" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>33</v>
-      </c>
-      <c r="R114" t="s">
-        <v>37</v>
-      </c>
-      <c r="S114" t="s">
-        <v>34</v>
-      </c>
-      <c r="U114" t="s">
-        <v>37</v>
-      </c>
-      <c r="X114">
+        <v>37</v>
+      </c>
+      <c r="P114" t="s">
+        <v>29</v>
+      </c>
+      <c r="W114" t="s">
+        <v>42</v>
+      </c>
+      <c r="X114" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB114">
         <v>9</v>
       </c>
     </row>
@@ -5463,7 +5793,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -5475,18 +5805,18 @@
         <v>-30</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I115" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>33</v>
-      </c>
-      <c r="X115">
+        <v>37</v>
+      </c>
+      <c r="AB115">
         <v>9</v>
       </c>
     </row>
@@ -5498,7 +5828,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -5510,24 +5840,27 @@
         <v>-30</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I116" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J116">
         <v>-5</v>
       </c>
       <c r="K116" t="s">
-        <v>33</v>
-      </c>
-      <c r="R116" t="s">
-        <v>37</v>
-      </c>
-      <c r="S116" t="s">
-        <v>34</v>
-      </c>
-      <c r="X116">
+        <v>37</v>
+      </c>
+      <c r="P116" t="s">
+        <v>29</v>
+      </c>
+      <c r="W116" t="s">
+        <v>42</v>
+      </c>
+      <c r="X116" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB116">
         <v>9</v>
       </c>
     </row>
@@ -5539,7 +5872,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -5551,30 +5884,33 @@
         <v>-25</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I117" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>33</v>
-      </c>
-      <c r="R117" t="s">
-        <v>39</v>
-      </c>
-      <c r="S117" t="s">
-        <v>55</v>
-      </c>
-      <c r="U117" t="s">
-        <v>37</v>
-      </c>
-      <c r="X117">
+        <v>37</v>
+      </c>
+      <c r="P117" t="s">
+        <v>44</v>
+      </c>
+      <c r="W117" t="s">
+        <v>45</v>
+      </c>
+      <c r="X117" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB117">
         <v>9</v>
       </c>
     </row>
@@ -5586,7 +5922,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -5598,36 +5934,39 @@
         <v>25</v>
       </c>
       <c r="G118" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H118" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I118" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J118">
         <v>10</v>
       </c>
       <c r="K118" t="s">
-        <v>33</v>
-      </c>
-      <c r="R118" t="s">
-        <v>30</v>
-      </c>
-      <c r="S118" t="s">
-        <v>74</v>
-      </c>
-      <c r="T118" t="s">
-        <v>63</v>
-      </c>
-      <c r="U118" t="s">
-        <v>37</v>
-      </c>
-      <c r="V118" t="s">
-        <v>37</v>
-      </c>
-      <c r="X118">
+        <v>37</v>
+      </c>
+      <c r="P118" t="s">
+        <v>49</v>
+      </c>
+      <c r="W118" t="s">
+        <v>34</v>
+      </c>
+      <c r="X118" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA118" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB118">
         <v>8</v>
       </c>
     </row>
@@ -5639,7 +5978,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5651,33 +5990,36 @@
         <v>15</v>
       </c>
       <c r="G119" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
-      </c>
-      <c r="R119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S119" t="s">
-        <v>88</v>
-      </c>
-      <c r="T119" t="s">
-        <v>80</v>
-      </c>
-      <c r="U119" t="s">
-        <v>30</v>
-      </c>
-      <c r="X119">
+        <v>56</v>
+      </c>
+      <c r="P119" t="s">
+        <v>29</v>
+      </c>
+      <c r="W119" t="s">
+        <v>34</v>
+      </c>
+      <c r="X119" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB119">
         <v>8</v>
       </c>
     </row>
@@ -5689,7 +6031,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -5701,33 +6043,36 @@
         <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H120" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I120" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>48</v>
-      </c>
-      <c r="R120" t="s">
-        <v>37</v>
-      </c>
-      <c r="S120" t="s">
-        <v>43</v>
-      </c>
-      <c r="T120" t="s">
-        <v>62</v>
-      </c>
-      <c r="U120" t="s">
-        <v>37</v>
-      </c>
-      <c r="X120">
+        <v>56</v>
+      </c>
+      <c r="P120" t="s">
+        <v>41</v>
+      </c>
+      <c r="W120" t="s">
+        <v>42</v>
+      </c>
+      <c r="X120" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB120">
         <v>8</v>
       </c>
     </row>
@@ -5739,7 +6084,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -5751,33 +6096,36 @@
         <v>15</v>
       </c>
       <c r="G121" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J121">
         <v>15</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
-      </c>
-      <c r="R121" t="s">
-        <v>30</v>
-      </c>
-      <c r="S121" t="s">
-        <v>60</v>
-      </c>
-      <c r="T121" t="s">
-        <v>61</v>
-      </c>
-      <c r="U121" t="s">
-        <v>37</v>
-      </c>
-      <c r="X121">
+        <v>37</v>
+      </c>
+      <c r="P121" t="s">
+        <v>68</v>
+      </c>
+      <c r="W121" t="s">
+        <v>34</v>
+      </c>
+      <c r="X121" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB121">
         <v>8</v>
       </c>
     </row>
@@ -5789,21 +6137,21 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F122">
         <v>3</v>
       </c>
       <c r="G122" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H122" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I122" t="s">
-        <v>68</v>
-      </c>
-      <c r="X122">
+        <v>78</v>
+      </c>
+      <c r="AB122">
         <v>8</v>
       </c>
     </row>
@@ -5815,19 +6163,19 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F123">
         <v>-40</v>
       </c>
       <c r="G123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I123" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
@@ -5838,7 +6186,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -5850,30 +6198,33 @@
         <v>-11</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I124" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J124">
         <v>15</v>
       </c>
       <c r="K124" t="s">
-        <v>48</v>
-      </c>
-      <c r="R124" t="s">
-        <v>30</v>
-      </c>
-      <c r="S124" t="s">
-        <v>90</v>
-      </c>
-      <c r="U124" t="s">
-        <v>30</v>
-      </c>
-      <c r="X124">
+        <v>56</v>
+      </c>
+      <c r="P124" t="s">
+        <v>100</v>
+      </c>
+      <c r="W124" t="s">
+        <v>34</v>
+      </c>
+      <c r="X124" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB124">
         <v>10</v>
       </c>
     </row>
@@ -5885,7 +6236,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -5897,30 +6248,33 @@
         <v>-26</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I125" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J125">
         <v>-1</v>
       </c>
       <c r="K125" t="s">
-        <v>33</v>
-      </c>
-      <c r="R125" t="s">
-        <v>37</v>
-      </c>
-      <c r="S125" t="s">
-        <v>84</v>
-      </c>
-      <c r="U125" t="s">
-        <v>30</v>
-      </c>
-      <c r="X125">
+        <v>37</v>
+      </c>
+      <c r="P125" t="s">
+        <v>102</v>
+      </c>
+      <c r="W125" t="s">
+        <v>42</v>
+      </c>
+      <c r="X125" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB125">
         <v>10</v>
       </c>
     </row>
@@ -5932,7 +6286,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -5944,30 +6298,33 @@
         <v>-25</v>
       </c>
       <c r="G126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H126" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I126" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J126">
         <v>9</v>
       </c>
       <c r="K126" t="s">
-        <v>48</v>
-      </c>
-      <c r="R126" t="s">
-        <v>37</v>
-      </c>
-      <c r="S126" t="s">
-        <v>84</v>
-      </c>
-      <c r="U126" t="s">
-        <v>37</v>
-      </c>
-      <c r="X126">
+        <v>56</v>
+      </c>
+      <c r="P126" t="s">
+        <v>102</v>
+      </c>
+      <c r="W126" t="s">
+        <v>42</v>
+      </c>
+      <c r="X126" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB126">
         <v>10</v>
       </c>
     </row>
@@ -5979,7 +6336,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D127">
         <v>3</v>
@@ -5991,30 +6348,33 @@
         <v>-34</v>
       </c>
       <c r="G127" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I127" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>33</v>
-      </c>
-      <c r="R127" t="s">
-        <v>30</v>
-      </c>
-      <c r="S127" t="s">
-        <v>38</v>
-      </c>
-      <c r="U127" t="s">
-        <v>30</v>
-      </c>
-      <c r="X127">
+        <v>37</v>
+      </c>
+      <c r="P127" t="s">
+        <v>41</v>
+      </c>
+      <c r="W127" t="s">
+        <v>34</v>
+      </c>
+      <c r="X127" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB127">
         <v>10</v>
       </c>
     </row>
@@ -6026,7 +6386,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>4</v>
@@ -6038,30 +6398,33 @@
         <v>-34</v>
       </c>
       <c r="G128" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H128" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I128" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J128">
         <v>12</v>
       </c>
       <c r="K128" t="s">
-        <v>48</v>
-      </c>
-      <c r="R128" t="s">
-        <v>37</v>
-      </c>
-      <c r="S128" t="s">
-        <v>84</v>
-      </c>
-      <c r="U128" t="s">
-        <v>30</v>
-      </c>
-      <c r="X128">
+        <v>56</v>
+      </c>
+      <c r="P128" t="s">
+        <v>41</v>
+      </c>
+      <c r="W128" t="s">
+        <v>42</v>
+      </c>
+      <c r="X128" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB128">
         <v>10</v>
       </c>
     </row>
@@ -6073,7 +6436,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6085,30 +6448,33 @@
         <v>-46</v>
       </c>
       <c r="G129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H129" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I129" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>33</v>
-      </c>
-      <c r="R129" t="s">
-        <v>37</v>
-      </c>
-      <c r="S129" t="s">
-        <v>84</v>
-      </c>
-      <c r="U129" t="s">
-        <v>37</v>
-      </c>
-      <c r="X129">
+        <v>37</v>
+      </c>
+      <c r="P129" t="s">
+        <v>102</v>
+      </c>
+      <c r="W129" t="s">
+        <v>42</v>
+      </c>
+      <c r="X129" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB129">
         <v>10</v>
       </c>
     </row>
@@ -6120,7 +6486,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -6132,30 +6498,33 @@
         <v>-46</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H130" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I130" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>33</v>
-      </c>
-      <c r="R130" t="s">
-        <v>37</v>
-      </c>
-      <c r="S130" t="s">
-        <v>84</v>
-      </c>
-      <c r="U130" t="s">
-        <v>30</v>
-      </c>
-      <c r="X130">
+        <v>37</v>
+      </c>
+      <c r="P130" t="s">
+        <v>102</v>
+      </c>
+      <c r="W130" t="s">
+        <v>42</v>
+      </c>
+      <c r="X130" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB130">
         <v>10</v>
       </c>
     </row>
@@ -6167,7 +6536,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D131">
         <v>3</v>
@@ -6179,30 +6548,33 @@
         <v>-46</v>
       </c>
       <c r="G131" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H131" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I131" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J131">
         <v>6</v>
       </c>
       <c r="K131" t="s">
-        <v>33</v>
-      </c>
-      <c r="R131" t="s">
-        <v>37</v>
-      </c>
-      <c r="S131" t="s">
-        <v>84</v>
-      </c>
-      <c r="U131" t="s">
-        <v>30</v>
-      </c>
-      <c r="X131">
+        <v>37</v>
+      </c>
+      <c r="P131" t="s">
+        <v>49</v>
+      </c>
+      <c r="W131" t="s">
+        <v>42</v>
+      </c>
+      <c r="X131" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB131">
         <v>10</v>
       </c>
     </row>
@@ -6214,7 +6586,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D132">
         <v>4</v>
@@ -6226,30 +6598,33 @@
         <v>48</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H132" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>33</v>
-      </c>
-      <c r="R132" t="s">
-        <v>39</v>
-      </c>
-      <c r="S132" t="s">
-        <v>55</v>
-      </c>
-      <c r="U132" t="s">
-        <v>30</v>
-      </c>
-      <c r="X132">
+        <v>37</v>
+      </c>
+      <c r="P132" t="s">
+        <v>44</v>
+      </c>
+      <c r="W132" t="s">
+        <v>45</v>
+      </c>
+      <c r="X132" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB132">
         <v>10</v>
       </c>
     </row>
@@ -6261,7 +6636,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6273,33 +6648,36 @@
         <v>47</v>
       </c>
       <c r="G133" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J133">
         <v>7</v>
       </c>
       <c r="K133" t="s">
-        <v>33</v>
-      </c>
-      <c r="R133" t="s">
-        <v>30</v>
-      </c>
-      <c r="S133" t="s">
-        <v>60</v>
-      </c>
-      <c r="T133" t="s">
-        <v>61</v>
-      </c>
-      <c r="U133" t="s">
-        <v>30</v>
-      </c>
-      <c r="X133">
+        <v>37</v>
+      </c>
+      <c r="P133" t="s">
+        <v>68</v>
+      </c>
+      <c r="W133" t="s">
+        <v>34</v>
+      </c>
+      <c r="X133" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB133">
         <v>9</v>
       </c>
     </row>
@@ -6311,7 +6689,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -6323,33 +6701,36 @@
         <v>40</v>
       </c>
       <c r="G134" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H134" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J134">
         <v>-1</v>
       </c>
       <c r="K134" t="s">
-        <v>48</v>
-      </c>
-      <c r="R134" t="s">
-        <v>37</v>
-      </c>
-      <c r="S134" t="s">
-        <v>60</v>
-      </c>
-      <c r="T134" t="s">
-        <v>61</v>
-      </c>
-      <c r="U134" t="s">
-        <v>30</v>
-      </c>
-      <c r="X134">
+        <v>56</v>
+      </c>
+      <c r="P134" t="s">
+        <v>68</v>
+      </c>
+      <c r="W134" t="s">
+        <v>42</v>
+      </c>
+      <c r="X134" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB134">
         <v>9</v>
       </c>
     </row>
@@ -6361,7 +6742,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D135">
         <v>3</v>
@@ -6373,33 +6754,36 @@
         <v>41</v>
       </c>
       <c r="G135" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I135" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J135">
         <v>7</v>
       </c>
       <c r="K135" t="s">
-        <v>33</v>
-      </c>
-      <c r="R135" t="s">
-        <v>30</v>
-      </c>
-      <c r="S135" t="s">
-        <v>60</v>
-      </c>
-      <c r="T135" t="s">
-        <v>61</v>
-      </c>
-      <c r="U135" t="s">
-        <v>30</v>
-      </c>
-      <c r="X135">
+        <v>37</v>
+      </c>
+      <c r="P135" t="s">
+        <v>68</v>
+      </c>
+      <c r="W135" t="s">
+        <v>34</v>
+      </c>
+      <c r="X135" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB135">
         <v>9</v>
       </c>
     </row>
@@ -6411,7 +6795,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -6423,33 +6807,36 @@
         <v>34</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H136" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I136" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J136">
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>48</v>
-      </c>
-      <c r="R136" t="s">
-        <v>37</v>
-      </c>
-      <c r="S136" t="s">
-        <v>60</v>
-      </c>
-      <c r="T136" t="s">
-        <v>61</v>
-      </c>
-      <c r="U136" t="s">
-        <v>37</v>
-      </c>
-      <c r="X136">
+        <v>56</v>
+      </c>
+      <c r="P136" t="s">
+        <v>68</v>
+      </c>
+      <c r="W136" t="s">
+        <v>42</v>
+      </c>
+      <c r="X136" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB136">
         <v>9</v>
       </c>
     </row>
@@ -6461,7 +6848,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -6473,33 +6860,36 @@
         <v>33</v>
       </c>
       <c r="G137" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H137" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I137" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>48</v>
-      </c>
-      <c r="R137" t="s">
-        <v>30</v>
-      </c>
-      <c r="S137" t="s">
-        <v>60</v>
-      </c>
-      <c r="T137" t="s">
-        <v>63</v>
-      </c>
-      <c r="U137" t="s">
-        <v>30</v>
-      </c>
-      <c r="X137">
+        <v>56</v>
+      </c>
+      <c r="P137" t="s">
+        <v>68</v>
+      </c>
+      <c r="W137" t="s">
+        <v>34</v>
+      </c>
+      <c r="X137" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB137">
         <v>9</v>
       </c>
     </row>
@@ -6511,7 +6901,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -6523,33 +6913,36 @@
         <v>33</v>
       </c>
       <c r="G138" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H138" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I138" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J138">
         <v>7</v>
       </c>
       <c r="K138" t="s">
-        <v>48</v>
-      </c>
-      <c r="R138" t="s">
-        <v>37</v>
-      </c>
-      <c r="S138" t="s">
-        <v>60</v>
-      </c>
-      <c r="T138" t="s">
-        <v>61</v>
-      </c>
-      <c r="U138" t="s">
-        <v>37</v>
-      </c>
-      <c r="X138">
+        <v>56</v>
+      </c>
+      <c r="P138" t="s">
+        <v>68</v>
+      </c>
+      <c r="W138" t="s">
+        <v>42</v>
+      </c>
+      <c r="X138" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB138">
         <v>9</v>
       </c>
     </row>
@@ -6561,7 +6954,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D139">
         <v>4</v>
@@ -6573,33 +6966,36 @@
         <v>26</v>
       </c>
       <c r="G139" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H139" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I139" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J139">
         <v>26</v>
       </c>
       <c r="K139" t="s">
-        <v>33</v>
-      </c>
-      <c r="R139" t="s">
-        <v>30</v>
-      </c>
-      <c r="S139" t="s">
-        <v>60</v>
-      </c>
-      <c r="T139" t="s">
-        <v>61</v>
-      </c>
-      <c r="U139" t="s">
-        <v>30</v>
-      </c>
-      <c r="X139">
+        <v>37</v>
+      </c>
+      <c r="P139" t="s">
+        <v>68</v>
+      </c>
+      <c r="W139" t="s">
+        <v>34</v>
+      </c>
+      <c r="X139" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB139">
         <v>9</v>
       </c>
     </row>
@@ -6611,21 +7007,21 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F140">
         <v>3</v>
       </c>
       <c r="G140" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H140" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I140" t="s">
-        <v>68</v>
-      </c>
-      <c r="X140">
+        <v>78</v>
+      </c>
+      <c r="AB140">
         <v>9</v>
       </c>
     </row>
@@ -6637,19 +7033,19 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F141">
         <v>-40</v>
       </c>
       <c r="G141" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H141" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I141" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142">
@@ -6660,7 +7056,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -6672,30 +7068,33 @@
         <v>-31</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H142" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J142">
         <v>7</v>
       </c>
       <c r="K142" t="s">
-        <v>48</v>
-      </c>
-      <c r="R142" t="s">
-        <v>37</v>
-      </c>
-      <c r="S142" t="s">
-        <v>34</v>
-      </c>
-      <c r="U142" t="s">
-        <v>30</v>
-      </c>
-      <c r="X142">
+        <v>56</v>
+      </c>
+      <c r="P142" t="s">
+        <v>29</v>
+      </c>
+      <c r="W142" t="s">
+        <v>42</v>
+      </c>
+      <c r="X142" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB142">
         <v>11</v>
       </c>
     </row>
@@ -6707,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -6719,27 +7118,30 @@
         <v>-38</v>
       </c>
       <c r="G143" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H143" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I143" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J143">
         <v>5</v>
       </c>
       <c r="K143" t="s">
-        <v>48</v>
-      </c>
-      <c r="R143" t="s">
-        <v>39</v>
-      </c>
-      <c r="U143" t="s">
-        <v>30</v>
-      </c>
-      <c r="X143">
+        <v>56</v>
+      </c>
+      <c r="P143" t="s">
+        <v>44</v>
+      </c>
+      <c r="W143" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB143">
         <v>11</v>
       </c>
     </row>
@@ -6751,7 +7153,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -6763,27 +7165,30 @@
         <v>-43</v>
       </c>
       <c r="G144" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H144" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I144" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>33</v>
-      </c>
-      <c r="R144" t="s">
-        <v>39</v>
-      </c>
-      <c r="U144" t="s">
-        <v>30</v>
-      </c>
-      <c r="X144">
+        <v>37</v>
+      </c>
+      <c r="P144" t="s">
+        <v>44</v>
+      </c>
+      <c r="W144" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB144">
         <v>11</v>
       </c>
     </row>
@@ -6795,7 +7200,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -6807,30 +7212,33 @@
         <v>-43</v>
       </c>
       <c r="G145" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H145" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I145" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J145">
         <v>5</v>
       </c>
       <c r="K145" t="s">
-        <v>48</v>
-      </c>
-      <c r="R145" t="s">
-        <v>37</v>
-      </c>
-      <c r="S145" t="s">
-        <v>84</v>
-      </c>
-      <c r="U145" t="s">
-        <v>37</v>
-      </c>
-      <c r="X145">
+        <v>56</v>
+      </c>
+      <c r="P145" t="s">
+        <v>29</v>
+      </c>
+      <c r="W145" t="s">
+        <v>42</v>
+      </c>
+      <c r="X145" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB145">
         <v>11</v>
       </c>
     </row>
@@ -6842,7 +7250,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D146">
         <v>3</v>
@@ -6854,30 +7262,33 @@
         <v>-48</v>
       </c>
       <c r="G146" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H146" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I146" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J146">
         <v>5</v>
       </c>
       <c r="K146" t="s">
-        <v>48</v>
-      </c>
-      <c r="R146" t="s">
-        <v>30</v>
-      </c>
-      <c r="S146" t="s">
-        <v>84</v>
-      </c>
-      <c r="U146" t="s">
-        <v>37</v>
-      </c>
-      <c r="X146">
+        <v>56</v>
+      </c>
+      <c r="P146" t="s">
+        <v>49</v>
+      </c>
+      <c r="W146" t="s">
+        <v>34</v>
+      </c>
+      <c r="X146" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB146">
         <v>11</v>
       </c>
     </row>
@@ -6889,7 +7300,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -6901,30 +7312,33 @@
         <v>47</v>
       </c>
       <c r="G147" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H147" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I147" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J147">
         <v>-2</v>
       </c>
       <c r="K147" t="s">
-        <v>33</v>
-      </c>
-      <c r="R147" t="s">
-        <v>30</v>
-      </c>
-      <c r="S147" t="s">
-        <v>84</v>
-      </c>
-      <c r="U147" t="s">
-        <v>37</v>
-      </c>
-      <c r="X147">
+        <v>37</v>
+      </c>
+      <c r="P147" t="s">
+        <v>41</v>
+      </c>
+      <c r="W147" t="s">
+        <v>34</v>
+      </c>
+      <c r="X147" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB147">
         <v>11</v>
       </c>
     </row>
@@ -6936,7 +7350,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D148">
         <v>2</v>
@@ -6948,30 +7362,33 @@
         <v>49</v>
       </c>
       <c r="G148" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H148" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I148" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>33</v>
-      </c>
-      <c r="R148" t="s">
-        <v>30</v>
-      </c>
-      <c r="S148" t="s">
-        <v>84</v>
-      </c>
-      <c r="U148" t="s">
-        <v>37</v>
-      </c>
-      <c r="X148">
+        <v>37</v>
+      </c>
+      <c r="P148" t="s">
+        <v>41</v>
+      </c>
+      <c r="W148" t="s">
+        <v>34</v>
+      </c>
+      <c r="X148" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB148">
         <v>11</v>
       </c>
     </row>
